--- a/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
+++ b/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
@@ -3,18 +3,42 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DDF59E73-7B7D-4FF3-9C82-00C86287DAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eclipse_coding_projects\selenium_automation\ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0D7D91-5939-413E-9F42-1D6B077CDF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="29070" windowHeight="19305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-255" yWindow="16080" windowWidth="29040" windowHeight="16440" tabRatio="916" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
-    <sheet name="Shoppage" sheetId="2" r:id="rId2"/>
-    <sheet name="SearchProductsPage" sheetId="3" r:id="rId3"/>
-    <sheet name="WishlistPage" sheetId="4" r:id="rId4"/>
+    <sheet name="HeaderElements" sheetId="9" r:id="rId2"/>
+    <sheet name="FooterElements" sheetId="10" r:id="rId3"/>
+    <sheet name="ShopPage" sheetId="2" r:id="rId4"/>
+    <sheet name="SearchProductsPage" sheetId="3" r:id="rId5"/>
+    <sheet name="WishlistPage" sheetId="4" r:id="rId6"/>
+    <sheet name="Loginpage" sheetId="5" r:id="rId7"/>
+    <sheet name="CartPage" sheetId="6" r:id="rId8"/>
+    <sheet name="AboutUsPage" sheetId="7" r:id="rId9"/>
+    <sheet name="ContactUsPage" sheetId="8" r:id="rId10"/>
+    <sheet name="CareersPage" sheetId="11" r:id="rId11"/>
+    <sheet name="AllBlogsPage" sheetId="12" r:id="rId12"/>
+    <sheet name="PrivacyPolicyPage" sheetId="15" r:id="rId13"/>
+    <sheet name="TermsOfServicePage" sheetId="17" r:id="rId14"/>
+    <sheet name="ResetPasswordPage" sheetId="24" r:id="rId15"/>
+    <sheet name="SingleBlogPage" sheetId="13" r:id="rId16"/>
+    <sheet name="HelpCenterPage" sheetId="14" r:id="rId17"/>
+    <sheet name="MyOrdersPage" sheetId="18" r:id="rId18"/>
+    <sheet name="UserDashboardPage" sheetId="19" r:id="rId19"/>
+    <sheet name="RegisterPage" sheetId="20" r:id="rId20"/>
+    <sheet name="ForgotPasswordPage" sheetId="21" r:id="rId21"/>
+    <sheet name="ThankYouPage" sheetId="22" r:id="rId22"/>
+    <sheet name="SingleProductPage" sheetId="25" r:id="rId23"/>
+    <sheet name="UpdateProfilePage" sheetId="23" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
   <si>
     <t>title</t>
   </si>
@@ -57,6 +81,141 @@
   </si>
   <si>
     <t>Shop | ECODERS</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/shop</t>
+  </si>
+  <si>
+    <t>Search-Products | ECODERS</t>
+  </si>
+  <si>
+    <t>Wishlist | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/wishlist</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>Cart | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/cart</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/login</t>
+  </si>
+  <si>
+    <t>Login | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/about-us</t>
+  </si>
+  <si>
+    <t>About Us | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/contact-us</t>
+  </si>
+  <si>
+    <t>Contact Us | ECODERS</t>
+  </si>
+  <si>
+    <t>Elements in homepage</t>
+  </si>
+  <si>
+    <t>Elements in footer section</t>
+  </si>
+  <si>
+    <t>Elements in header</t>
+  </si>
+  <si>
+    <t>Careers | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/careers</t>
+  </si>
+  <si>
+    <t>All Blogs | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/all-blogs</t>
+  </si>
+  <si>
+    <t>Blog Details | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/single-blog/python-lists-basics-and-common-operations/6964604f3ba568c4af228fb5</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/help-center</t>
+  </si>
+  <si>
+    <t>Help Center | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/privacy-policy</t>
+  </si>
+  <si>
+    <t>Privacy Policy | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/terms-of-service</t>
+  </si>
+  <si>
+    <t>Terms Of Service | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/my-orders</t>
+  </si>
+  <si>
+    <t>Myorders | ECODERS</t>
+  </si>
+  <si>
+    <t>User Dashboard | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/dashboard</t>
+  </si>
+  <si>
+    <t>Register | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/register</t>
+  </si>
+  <si>
+    <t>Forgot Password | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/forgot-password</t>
+  </si>
+  <si>
+    <t>Update Profile | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/update-profile/695ed930fce74c23cb5ca1e8</t>
+  </si>
+  <si>
+    <t>Thank You | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/reset-password</t>
+  </si>
+  <si>
+    <t>Reset Password | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/thank-you</t>
+  </si>
+  <si>
+    <t>Single-Product | ECODERS</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/single-product/&lt;id of the product&gt;</t>
   </si>
 </sst>
 </file>
@@ -386,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
@@ -425,10 +584,9 @@
         <v>49290</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E12">
-        <f>(E4+E5+E6+E7+E8+E9+E10+E11)</f>
-        <v>0</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +598,547 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA97BC37-EFFF-480A-BC59-DFD0E7100464}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525F1383-2A78-4B0A-ADE7-DA91AD8B5E35}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33161DF6-B939-4FAF-B688-45D8E4D6BED9}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54301956-4CAC-44C6-8685-DDD5B1CAC33C}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4390A0A-1392-455B-A9DD-E4EFE75B0261}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F08B5E-9142-4700-BF83-13A8F3F275CD}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B939DD3-F1DE-40E2-9A38-092BAE87BCA3}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="97.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6B6493-0D3D-4389-A1A0-65B0B00E2BE7}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB58B7E-2561-451D-A170-D29DCAFE6EEB}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB8F8C3-5C71-4A1A-B2C1-A3F51A888DB4}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B827425-D17D-4733-BD3A-36E5F4654BB8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA9F15F-8CA3-44A0-9CDA-87680CF611FF}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B10798F-7412-4934-B91C-D4E706AAF248}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ACEB178-EB9F-4870-8F43-F13577AB796A}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5160B6A-1952-4006-8274-E06B2E7ED85F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{D5D2864C-1291-4BC5-AAE4-2F3905AC57CF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87A8DBC-CACE-41F2-99C7-7AAAECAE7D18}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3666F903-4803-4868-9EAC-6EC0868004A0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECF4EDD-40F8-4043-B6B3-4E5FD85806A7}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{E391B97E-DC1D-4208-AADA-063EAD4396BC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3146659-BA30-470B-AE8C-F36F71E851DF}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -452,28 +1147,135 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3146659-BA30-470B-AE8C-F36F71E851DF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F0863A-930D-482B-9098-A5EF498D9BCE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB2E2EB-CE6F-400C-8399-0962447D7D19}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F775A6-098A-4ECB-A8AA-90B79B2CE092}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{8DD9572A-687C-4FF7-BA3A-72FB059042CC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47357344-828C-4EC6-B852-3C91B59E4E69}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{5C8209E6-CB32-4237-8198-C1FC50719F5D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
+++ b/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eclipse_coding_projects\selenium_automation\ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0D7D91-5939-413E-9F42-1D6B077CDF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683F844E-ADD6-4416-93AC-FB3D6E76092E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-255" yWindow="16080" windowWidth="29040" windowHeight="16440" tabRatio="916" firstSheet="11" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="916" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
   <si>
     <t>title</t>
   </si>
@@ -216,6 +216,24 @@
   </si>
   <si>
     <t>http://localhost:5173/single-product/&lt;id of the product&gt;</t>
+  </si>
+  <si>
+    <t>product names</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>samsung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  yoga mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pen    </t>
+  </si>
+  <si>
+    <t>water bottle</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3146659-BA30-470B-AE8C-F36F71E851DF}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
@@ -1148,6 +1166,36 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
+++ b/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eclipse_coding_projects\selenium_automation\ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683F844E-ADD6-4416-93AC-FB3D6E76092E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="916" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="916"/>
   </bookViews>
   <sheets>
     <sheet name="Homepage" sheetId="1" r:id="rId1"/>
@@ -38,9 +32,9 @@
     <sheet name="SingleProductPage" sheetId="25" r:id="rId23"/>
     <sheet name="UpdateProfilePage" sheetId="23" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -57,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>title</t>
   </si>
@@ -235,12 +229,21 @@
   <si>
     <t>water bottle</t>
   </si>
+  <si>
+    <t>Explore Categories</t>
+  </si>
+  <si>
+    <t>Tap any category to instantly search products.</t>
+  </si>
+  <si>
+    <t>Showing 7 of 10 categories</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,7 +346,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -378,7 +381,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -555,24 +558,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
     <col min="2" max="2" width="21.7109375" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="41.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -580,7 +585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -596,44 +601,53 @@
       <c r="E2">
         <v>12345</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="D4" s="2">
         <v>49290</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{87BA9A14-DFF5-4EAF-A050-D295A79426E2}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{DD79F5A1-9BC0-41FA-8AE6-BACD824FB755}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA97BC37-EFFF-480A-BC59-DFD0E7100464}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -647,23 +661,23 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525F1383-2A78-4B0A-ADE7-DA91AD8B5E35}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -677,23 +691,23 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33161DF6-B939-4FAF-B688-45D8E4D6BED9}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -707,23 +721,23 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54301956-4CAC-44C6-8685-DDD5B1CAC33C}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -737,23 +751,23 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4390A0A-1392-455B-A9DD-E4EFE75B0261}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -767,11 +781,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F08B5E-9142-4700-BF83-13A8F3F275CD}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -779,7 +793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -793,23 +807,23 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B939DD3-F1DE-40E2-9A38-092BAE87BCA3}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="97.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -823,23 +837,23 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F6B6493-0D3D-4389-A1A0-65B0B00E2BE7}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -853,23 +867,23 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB58B7E-2561-451D-A170-D29DCAFE6EEB}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -883,23 +897,23 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB8F8C3-5C71-4A1A-B2C1-A3F51A888DB4}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -913,14 +927,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B827425-D17D-4733-BD3A-36E5F4654BB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -931,23 +945,23 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA9F15F-8CA3-44A0-9CDA-87680CF611FF}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -961,23 +975,23 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B10798F-7412-4934-B91C-D4E706AAF248}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -991,23 +1005,23 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ACEB178-EB9F-4870-8F43-F13577AB796A}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1021,23 +1035,23 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5160B6A-1952-4006-8274-E06B2E7ED85F}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1047,30 +1061,30 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{D5D2864C-1291-4BC5-AAE4-2F3905AC57CF}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C87A8DBC-CACE-41F2-99C7-7AAAECAE7D18}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -1078,7 +1092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1086,7 +1100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -1100,14 +1114,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3666F903-4803-4868-9EAC-6EC0868004A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>23</v>
       </c>
@@ -1118,15 +1132,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECF4EDD-40F8-4043-B6B3-4E5FD85806A7}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1134,7 +1148,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1144,56 +1158,56 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{E391B97E-DC1D-4208-AADA-063EAD4396BC}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3146659-BA30-470B-AE8C-F36F71E851DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -1204,15 +1218,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F0863A-930D-482B-9098-A5EF498D9BCE}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1220,7 +1234,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1234,15 +1248,15 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB2E2EB-CE6F-400C-8399-0962447D7D19}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.28515625" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1250,7 +1264,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1264,22 +1278,22 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F775A6-098A-4ECB-A8AA-90B79B2CE092}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1289,30 +1303,30 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{8DD9572A-687C-4FF7-BA3A-72FB059042CC}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47357344-828C-4EC6-B852-3C91B59E4E69}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1322,7 +1336,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{5C8209E6-CB32-4237-8198-C1FC50719F5D}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
+++ b/ecommerse_mavne_project_setup_anjan_bharath_Shilpa_sharnya/project_documents.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>title</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Contact Us | ECODERS</t>
   </si>
   <si>
-    <t>Elements in homepage</t>
-  </si>
-  <si>
     <t>Elements in footer section</t>
   </si>
   <si>
@@ -237,6 +234,27 @@
   </si>
   <si>
     <t>Showing 7 of 10 categories</t>
+  </si>
+  <si>
+    <t>All Brand Names</t>
+  </si>
+  <si>
+    <t>APPLE</t>
+  </si>
+  <si>
+    <t>SAMSUNG</t>
+  </si>
+  <si>
+    <t>SONY</t>
+  </si>
+  <si>
+    <t>Popular Brands</t>
+  </si>
+  <si>
+    <t>Smooth infinite marquee • drag / swipe anytime • tap to search</t>
+  </si>
+  <si>
+    <t>117 brands</t>
   </si>
 </sst>
 </file>
@@ -558,7 +576,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -566,18 +584,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="41.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="58.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -602,23 +625,47 @@
         <v>12345</v>
       </c>
       <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
         <v>59</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>60</v>
       </c>
-      <c r="H2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="D4" s="2">
         <v>49290</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>22</v>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -679,10 +726,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -709,10 +756,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
         <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -739,10 +786,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
         <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -769,11 +816,11 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
         <v>35</v>
       </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -795,10 +842,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" t="s">
         <v>48</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -825,10 +872,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -855,10 +902,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
         <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -885,10 +932,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
         <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -915,11 +962,11 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
         <v>39</v>
       </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -936,7 +983,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -963,10 +1010,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -993,10 +1040,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" t="s">
         <v>43</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1023,10 +1070,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1053,10 +1100,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1086,10 +1133,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
         <v>45</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1102,11 +1149,11 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1123,7 +1170,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1184,32 +1231,32 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
